--- a/data/news/prob_markets_with_llm_stances.xlsx
+++ b/data/news/prob_markets_with_llm_stances.xlsx
@@ -1214,7 +1214,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1225,6 +1225,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1261,15 +1267,6 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1277,6 +1274,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1897,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>74</v>
@@ -1936,7 +1942,7 @@
         <v>83</v>
       </c>
       <c r="S2" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>84</v>
@@ -1975,7 +1981,7 @@
         <v>93</v>
       </c>
       <c r="AF2" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>94</v>
@@ -2014,7 +2020,7 @@
         <v>103</v>
       </c>
       <c r="AS2" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>104</v>
@@ -2029,7 +2035,7 @@
         <v>107</v>
       </c>
       <c r="AX2" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AY2" s="1" t="s">
         <v>108</v>
@@ -2109,7 +2115,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>117</v>
@@ -2148,7 +2154,7 @@
         <v>123</v>
       </c>
       <c r="S3" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>124</v>
@@ -2187,7 +2193,7 @@
         <v>130</v>
       </c>
       <c r="AF3" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AG3" s="1" t="s">
         <v>131</v>
@@ -2226,7 +2232,7 @@
         <v>137</v>
       </c>
       <c r="AS3" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>138</v>
@@ -2241,7 +2247,7 @@
         <v>107</v>
       </c>
       <c r="AX3" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>108</v>
@@ -2321,7 +2327,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>147</v>
@@ -2360,7 +2366,7 @@
         <v>152</v>
       </c>
       <c r="S4" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>153</v>
@@ -2399,7 +2405,7 @@
         <v>159</v>
       </c>
       <c r="AF4" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>160</v>
@@ -2438,7 +2444,7 @@
         <v>166</v>
       </c>
       <c r="AS4" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AT4" s="1" t="s">
         <v>167</v>
@@ -2453,7 +2459,7 @@
         <v>107</v>
       </c>
       <c r="AX4" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AY4" s="1" t="s">
         <v>108</v>
@@ -2533,7 +2539,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>175</v>
@@ -2572,7 +2578,7 @@
         <v>181</v>
       </c>
       <c r="S5" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>182</v>
@@ -2611,7 +2617,7 @@
         <v>188</v>
       </c>
       <c r="AF5" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AG5" s="1" t="s">
         <v>189</v>
@@ -2650,7 +2656,7 @@
         <v>195</v>
       </c>
       <c r="AS5" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>196</v>
@@ -2665,7 +2671,7 @@
         <v>107</v>
       </c>
       <c r="AX5" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AY5" s="1" t="s">
         <v>108</v>
@@ -2745,7 +2751,7 @@
         <v>37</v>
       </c>
       <c r="F6" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>205</v>
@@ -2784,7 +2790,7 @@
         <v>211</v>
       </c>
       <c r="S6" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>212</v>
@@ -2823,7 +2829,7 @@
         <v>218</v>
       </c>
       <c r="AF6" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AG6" s="1" t="s">
         <v>219</v>
@@ -2862,7 +2868,7 @@
         <v>225</v>
       </c>
       <c r="AS6" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AT6" s="1" t="s">
         <v>226</v>
@@ -2877,7 +2883,7 @@
         <v>107</v>
       </c>
       <c r="AX6" s="6">
-        <v>25569.041962604166</v>
+        <v>25569.04196759259</v>
       </c>
       <c r="AY6" s="1" t="s">
         <v>108</v>

--- a/data/news/prob_markets_with_llm_stances.xlsx
+++ b/data/news/prob_markets_with_llm_stances.xlsx
@@ -1214,19 +1214,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1262,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -1274,15 +1268,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1602,79 +1587,79 @@
   <dimension ref="A1:BR6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="63" max="63" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="64" max="64" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="65" max="65" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="66" max="66" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="67" max="67" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="68" max="68" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="69" max="69" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="70" max="70" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="23.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="63" max="63" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="64" max="64" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="65" max="65" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="66" max="66" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="67" max="67" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="68" max="68" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="69" max="69" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="70" max="70" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,11 +1884,11 @@
       <c r="D2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>9</v>
       </c>
-      <c r="F2" s="6">
-        <v>25569.04196759259</v>
+      <c r="F2" s="3">
+        <v>46009</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>74</v>
@@ -1920,10 +1905,10 @@
       <c r="K2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <v>5</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>5</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -1941,8 +1926,8 @@
       <c r="R2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S2" s="6">
-        <v>25569.04196759259</v>
+      <c r="S2" s="3">
+        <v>46038</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>84</v>
@@ -1959,10 +1944,10 @@
       <c r="X2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="2">
         <v>5</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="2">
         <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1980,8 +1965,8 @@
       <c r="AE2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AF2" s="6">
-        <v>25569.04196759259</v>
+      <c r="AF2" s="3">
+        <v>46120</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>94</v>
@@ -1998,10 +1983,10 @@
       <c r="AK2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AL2" s="5">
+      <c r="AL2" s="2">
         <v>3</v>
       </c>
-      <c r="AM2" s="5">
+      <c r="AM2" s="2">
         <v>2</v>
       </c>
       <c r="AN2" s="1" t="s">
@@ -2019,8 +2004,8 @@
       <c r="AR2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="6">
-        <v>25569.04196759259</v>
+      <c r="AS2" s="3">
+        <v>46127</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>104</v>
@@ -2034,43 +2019,43 @@
       <c r="AW2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX2" s="6">
-        <v>25569.04196759259</v>
+      <c r="AX2" s="3">
+        <v>46122</v>
       </c>
       <c r="AY2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AZ2" s="5">
+      <c r="AZ2" s="2">
         <v>45</v>
       </c>
-      <c r="BA2" s="7">
+      <c r="BA2" s="4">
         <v>42.5</v>
       </c>
-      <c r="BB2" s="7">
+      <c r="BB2" s="4">
         <v>32.5</v>
       </c>
-      <c r="BC2" s="5">
+      <c r="BC2" s="2">
         <v>25</v>
       </c>
-      <c r="BD2" s="5">
+      <c r="BD2" s="2">
         <v>5</v>
       </c>
-      <c r="BE2" s="5">
+      <c r="BE2" s="2">
         <v>5</v>
       </c>
-      <c r="BF2" s="5">
+      <c r="BF2" s="2">
         <v>5</v>
       </c>
-      <c r="BG2" s="5">
+      <c r="BG2" s="2">
         <v>5</v>
       </c>
-      <c r="BH2" s="5">
+      <c r="BH2" s="2">
         <v>5</v>
       </c>
-      <c r="BI2" s="5">
+      <c r="BI2" s="2">
         <v>12</v>
       </c>
-      <c r="BJ2" s="5">
+      <c r="BJ2" s="2">
         <v>0</v>
       </c>
       <c r="BK2" s="1" t="s">
@@ -2111,11 +2096,11 @@
       <c r="D3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>12</v>
       </c>
-      <c r="F3" s="6">
-        <v>25569.04196759259</v>
+      <c r="F3" s="3">
+        <v>45975</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>117</v>
@@ -2132,10 +2117,10 @@
       <c r="K3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="2">
         <v>5</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="2">
         <v>5</v>
       </c>
       <c r="N3" s="1" t="s">
@@ -2153,8 +2138,8 @@
       <c r="R3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="S3" s="6">
-        <v>25569.04196759259</v>
+      <c r="S3" s="3">
+        <v>46112</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>124</v>
@@ -2171,10 +2156,10 @@
       <c r="X3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Y3" s="5">
+      <c r="Y3" s="2">
         <v>3</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3" s="2">
         <v>3</v>
       </c>
       <c r="AA3" s="1" t="s">
@@ -2192,8 +2177,8 @@
       <c r="AE3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AF3" s="6">
-        <v>25569.04196759259</v>
+      <c r="AF3" s="3">
+        <v>46125</v>
       </c>
       <c r="AG3" s="1" t="s">
         <v>131</v>
@@ -2210,10 +2195,10 @@
       <c r="AK3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AL3" s="5">
+      <c r="AL3" s="2">
         <v>2</v>
       </c>
-      <c r="AM3" s="5">
+      <c r="AM3" s="2">
         <v>2</v>
       </c>
       <c r="AN3" s="1" t="s">
@@ -2231,8 +2216,8 @@
       <c r="AR3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AS3" s="6">
-        <v>25569.04196759259</v>
+      <c r="AS3" s="3">
+        <v>46126</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>138</v>
@@ -2246,43 +2231,43 @@
       <c r="AW3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX3" s="6">
-        <v>25569.04196759259</v>
+      <c r="AX3" s="3">
+        <v>46122</v>
       </c>
       <c r="AY3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AZ3" s="5">
+      <c r="AZ3" s="2">
         <v>25</v>
       </c>
-      <c r="BA3" s="5">
+      <c r="BA3" s="2">
         <v>45</v>
       </c>
-      <c r="BB3" s="5">
+      <c r="BB3" s="2">
         <v>45</v>
       </c>
-      <c r="BC3" s="5">
+      <c r="BC3" s="2">
         <v>45</v>
       </c>
-      <c r="BD3" s="5">
+      <c r="BD3" s="2">
         <v>67</v>
       </c>
-      <c r="BE3" s="5">
+      <c r="BE3" s="2">
         <v>67</v>
       </c>
-      <c r="BF3" s="5">
+      <c r="BF3" s="2">
         <v>67</v>
       </c>
-      <c r="BG3" s="5">
+      <c r="BG3" s="2">
         <v>5</v>
       </c>
-      <c r="BH3" s="5">
+      <c r="BH3" s="2">
         <v>20</v>
       </c>
-      <c r="BI3" s="7">
+      <c r="BI3" s="4">
         <v>23.5</v>
       </c>
-      <c r="BJ3" s="5">
+      <c r="BJ3" s="2">
         <v>0</v>
       </c>
       <c r="BK3" s="1" t="s">
@@ -2323,11 +2308,11 @@
       <c r="D4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>16</v>
       </c>
-      <c r="F4" s="6">
-        <v>25569.04196759259</v>
+      <c r="F4" s="3">
+        <v>45981</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>147</v>
@@ -2344,10 +2329,10 @@
       <c r="K4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="2">
         <v>5</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="2">
         <v>5</v>
       </c>
       <c r="N4" s="1" t="s">
@@ -2365,8 +2350,8 @@
       <c r="R4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="S4" s="6">
-        <v>25569.04196759259</v>
+      <c r="S4" s="3">
+        <v>45996</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>153</v>
@@ -2383,10 +2368,10 @@
       <c r="X4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="Y4" s="2">
         <v>5</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="2">
         <v>5</v>
       </c>
       <c r="AA4" s="1" t="s">
@@ -2404,8 +2389,8 @@
       <c r="AE4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AF4" s="6">
-        <v>25569.04196759259</v>
+      <c r="AF4" s="3">
+        <v>46059</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>160</v>
@@ -2422,10 +2407,10 @@
       <c r="AK4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AL4" s="5">
+      <c r="AL4" s="2">
         <v>3</v>
       </c>
-      <c r="AM4" s="5">
+      <c r="AM4" s="2">
         <v>3</v>
       </c>
       <c r="AN4" s="1" t="s">
@@ -2443,8 +2428,8 @@
       <c r="AR4" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AS4" s="6">
-        <v>25569.04196759259</v>
+      <c r="AS4" s="3">
+        <v>46127</v>
       </c>
       <c r="AT4" s="1" t="s">
         <v>167</v>
@@ -2458,43 +2443,43 @@
       <c r="AW4" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX4" s="6">
-        <v>25569.04196759259</v>
+      <c r="AX4" s="3">
+        <v>46122</v>
       </c>
       <c r="AY4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AZ4" s="5">
+      <c r="AZ4" s="2">
         <v>40</v>
       </c>
-      <c r="BA4" s="5">
+      <c r="BA4" s="2">
         <v>67</v>
       </c>
-      <c r="BB4" s="5">
+      <c r="BB4" s="2">
         <v>67</v>
       </c>
-      <c r="BC4" s="5">
+      <c r="BC4" s="2">
         <v>67</v>
       </c>
-      <c r="BD4" s="5">
+      <c r="BD4" s="2">
         <v>67</v>
       </c>
-      <c r="BE4" s="5">
+      <c r="BE4" s="2">
         <v>67</v>
       </c>
-      <c r="BF4" s="5">
+      <c r="BF4" s="2">
         <v>67</v>
       </c>
-      <c r="BG4" s="5">
+      <c r="BG4" s="2">
         <v>45</v>
       </c>
-      <c r="BH4" s="5">
+      <c r="BH4" s="2">
         <v>45</v>
       </c>
-      <c r="BI4" s="5">
+      <c r="BI4" s="2">
         <v>45</v>
       </c>
-      <c r="BJ4" s="5">
+      <c r="BJ4" s="2">
         <v>0</v>
       </c>
       <c r="BK4" s="1" t="s">
@@ -2535,11 +2520,11 @@
       <c r="D5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>17</v>
       </c>
-      <c r="F5" s="6">
-        <v>25569.04196759259</v>
+      <c r="F5" s="3">
+        <v>46120</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>175</v>
@@ -2556,10 +2541,10 @@
       <c r="K5" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="2">
         <v>4</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="2">
         <v>4</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -2577,8 +2562,8 @@
       <c r="R5" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="S5" s="6">
-        <v>25569.04196759259</v>
+      <c r="S5" s="3">
+        <v>46121</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>182</v>
@@ -2595,10 +2580,10 @@
       <c r="X5" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="Y5" s="2">
         <v>4</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="2">
         <v>4</v>
       </c>
       <c r="AA5" s="1" t="s">
@@ -2616,8 +2601,8 @@
       <c r="AE5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="AF5" s="6">
-        <v>25569.04196759259</v>
+      <c r="AF5" s="3">
+        <v>46121</v>
       </c>
       <c r="AG5" s="1" t="s">
         <v>189</v>
@@ -2634,10 +2619,10 @@
       <c r="AK5" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="AL5" s="5">
+      <c r="AL5" s="2">
         <v>4</v>
       </c>
-      <c r="AM5" s="5">
+      <c r="AM5" s="2">
         <v>2</v>
       </c>
       <c r="AN5" s="1" t="s">
@@ -2655,8 +2640,8 @@
       <c r="AR5" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AS5" s="6">
-        <v>25569.04196759259</v>
+      <c r="AS5" s="3">
+        <v>46126</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>196</v>
@@ -2670,43 +2655,43 @@
       <c r="AW5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX5" s="6">
-        <v>25569.04196759259</v>
+      <c r="AX5" s="3">
+        <v>46122</v>
       </c>
       <c r="AY5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AZ5" s="5">
+      <c r="AZ5" s="2">
         <v>5</v>
       </c>
-      <c r="BA5" s="5">
+      <c r="BA5" s="2">
         <v>45</v>
       </c>
-      <c r="BB5" s="5">
+      <c r="BB5" s="2">
         <v>45</v>
       </c>
-      <c r="BC5" s="5">
+      <c r="BC5" s="2">
         <v>40</v>
       </c>
-      <c r="BD5" s="5">
+      <c r="BD5" s="2">
         <v>67</v>
       </c>
-      <c r="BE5" s="5">
+      <c r="BE5" s="2">
         <v>67</v>
       </c>
-      <c r="BF5" s="5">
+      <c r="BF5" s="2">
         <v>60</v>
       </c>
-      <c r="BG5" s="5">
+      <c r="BG5" s="2">
         <v>40</v>
       </c>
-      <c r="BH5" s="5">
+      <c r="BH5" s="2">
         <v>45</v>
       </c>
-      <c r="BI5" s="7">
+      <c r="BI5" s="4">
         <v>24.5</v>
       </c>
-      <c r="BJ5" s="5">
+      <c r="BJ5" s="2">
         <v>0</v>
       </c>
       <c r="BK5" s="1" t="s">
@@ -2747,11 +2732,11 @@
       <c r="D6" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <v>37</v>
       </c>
-      <c r="F6" s="6">
-        <v>25569.04196759259</v>
+      <c r="F6" s="3">
+        <v>45997</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>205</v>
@@ -2768,10 +2753,10 @@
       <c r="K6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="2">
         <v>1</v>
       </c>
       <c r="N6" s="1" t="s">
@@ -2789,8 +2774,8 @@
       <c r="R6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="S6" s="6">
-        <v>25569.04196759259</v>
+      <c r="S6" s="3">
+        <v>46112</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>212</v>
@@ -2807,10 +2792,10 @@
       <c r="X6" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="Y6" s="5">
+      <c r="Y6" s="2">
         <v>4</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6" s="2">
         <v>1</v>
       </c>
       <c r="AA6" s="1" t="s">
@@ -2828,8 +2813,8 @@
       <c r="AE6" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AF6" s="6">
-        <v>25569.04196759259</v>
+      <c r="AF6" s="3">
+        <v>46112</v>
       </c>
       <c r="AG6" s="1" t="s">
         <v>219</v>
@@ -2846,10 +2831,10 @@
       <c r="AK6" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AL6" s="5">
+      <c r="AL6" s="2">
         <v>1</v>
       </c>
-      <c r="AM6" s="5">
+      <c r="AM6" s="2">
         <v>1</v>
       </c>
       <c r="AN6" s="1" t="s">
@@ -2867,8 +2852,8 @@
       <c r="AR6" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AS6" s="6">
-        <v>25569.04196759259</v>
+      <c r="AS6" s="3">
+        <v>46123</v>
       </c>
       <c r="AT6" s="1" t="s">
         <v>226</v>
@@ -2882,43 +2867,43 @@
       <c r="AW6" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX6" s="6">
-        <v>25569.04196759259</v>
+      <c r="AX6" s="3">
+        <v>46122</v>
       </c>
       <c r="AY6" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AZ6" s="5">
+      <c r="AZ6" s="2">
         <v>5</v>
       </c>
-      <c r="BA6" s="5">
+      <c r="BA6" s="2">
         <v>0</v>
       </c>
-      <c r="BB6" s="5">
+      <c r="BB6" s="2">
         <v>0</v>
       </c>
-      <c r="BC6" s="5">
+      <c r="BC6" s="2">
         <v>0</v>
       </c>
-      <c r="BD6" s="5">
+      <c r="BD6" s="2">
         <v>0</v>
       </c>
-      <c r="BE6" s="5">
+      <c r="BE6" s="2">
         <v>0</v>
       </c>
-      <c r="BF6" s="7">
+      <c r="BF6" s="4">
         <v>2.5</v>
       </c>
-      <c r="BG6" s="5">
+      <c r="BG6" s="2">
         <v>0</v>
       </c>
-      <c r="BH6" s="5">
+      <c r="BH6" s="2">
         <v>0</v>
       </c>
-      <c r="BI6" s="5">
+      <c r="BI6" s="2">
         <v>0</v>
       </c>
-      <c r="BJ6" s="5">
+      <c r="BJ6" s="2">
         <v>0</v>
       </c>
       <c r="BK6" s="1" t="s">
